--- a/output/pdf_financials_xlsx/GRG.xlsx
+++ b/output/pdf_financials_xlsx/GRG.xlsx
@@ -3692,31 +3692,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>17.61165</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>18.484549</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>18.764786</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>26.896681</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>26.722172</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>26.691634</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>26.983361</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>27.334603</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>29.76193</v>
       </c>
     </row>
     <row r="93">
@@ -6089,7 +6089,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7031,7 +7035,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -7644,7 +7652,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>17.61165</v>
       </c>
@@ -8065,7 +8077,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GRG.xlsx
+++ b/output/pdf_financials_xlsx/GRG.xlsx
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.128131</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.103647</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009251000000000001</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005165</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.140109</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.027981</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.012936</v>
       </c>
     </row>
     <row r="13">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.336549</v>
+        <v>-2.46468</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-17.800975</v>
+        <v>-17.904622</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-19.839184</v>
+        <v>-19.848435</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.046627</v>
+        <v>-6.051792</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.818037</v>
+        <v>-5.958146</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-8.366453</v>
+        <v>-8.394434</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.391672</v>
+        <v>-1.404608</v>
       </c>
     </row>
     <row r="28">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.330425</v>
+        <v>-2.458556</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-17.794738</v>
+        <v>-17.898385</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-19.808554</v>
+        <v>-19.817805</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.936954</v>
+        <v>-5.942119</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.699577</v>
+        <v>-5.839686</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.343546</v>
+        <v>-8.371527</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.391672</v>
+        <v>-1.404608</v>
       </c>
     </row>
     <row r="30">
@@ -4870,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023237</v>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
@@ -4878,13 +4878,13 @@
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.143758</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.146148</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03027</v>
       </c>
       <c r="J124" s="3" t="n">
         <v>0</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023237</v>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
@@ -4916,13 +4916,13 @@
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.143758</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.146148</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03027</v>
       </c>
       <c r="J125" s="3" t="n">
         <v>0</v>
@@ -10028,7 +10028,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -14691,7 +14695,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14756,7 +14760,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -16116,7 +16120,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -16238,7 +16242,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -16966,7 +16970,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -17090,7 +17094,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -18046,7 +18050,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -18109,7 +18113,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
